--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405966.5087274795</v>
+        <v>405967</v>
       </c>
       <c r="R2" t="n">
-        <v>6254384.8669718</v>
+        <v>6254385</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99108</v>
+        <v>99113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99113</v>
+        <v>99114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99114</v>
+        <v>99141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99141</v>
+        <v>99147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99147</v>
+        <v>99154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99154</v>
+        <v>99158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99158</v>
+        <v>99165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99168</v>
+        <v>99173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99173</v>
+        <v>99181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 6614-2025 artfynd.xlsx
+++ b/artfynd/A 6614-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74528450</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
